--- a/dataset/construct/dataset_splits/data_size/10_percent/tum/fold4.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/tum/fold4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2220</v>
+        <v>573</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,77 +625,79 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.7674595659999</v>
+        <v>74.9002794889345</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>41.659990386156</v>
       </c>
       <c r="E2" t="n">
-        <v>17.7999288002847</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>217.2</v>
+      </c>
+      <c r="I2" t="n">
+        <v>183.2</v>
+      </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>124.3</v>
       </c>
       <c r="K2" t="n">
-        <v>30.9</v>
+        <v>524.6999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="M2" t="n">
-        <v>19.3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>56.2</v>
+        <v>12.2</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>21.05</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>21.5495289024701</v>
       </c>
       <c r="X2" t="n">
-        <v>20.25</v>
+        <v>20.9523162086917</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0896226415094339</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.6582633053221</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.4418823263722</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -728,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -737,24 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>164</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>683</v>
+        <v>501</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,79 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>77.1018803711309</v>
+        <v>80.7024477463432</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>24.7675659198292</v>
       </c>
       <c r="E3" t="n">
-        <v>24.5674740484429</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="I3" t="n">
-        <v>1120</v>
+        <v>73</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>553</v>
+        <v>110</v>
       </c>
       <c r="L3" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>537</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1552</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>20.0534759358289</v>
       </c>
       <c r="X3" t="n">
-        <v>25.3</v>
+        <v>19.9279552640389</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.255172413793103</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.8281130634072</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.8794571386939</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -852,33 +830,24 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>176</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2257</v>
+        <v>452</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,77 +855,79 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68.1240494207418</v>
+        <v>75.6426521345096</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>31.4359113034072</v>
       </c>
       <c r="E4" t="n">
-        <v>24.4897959183673</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>679</v>
+      </c>
+      <c r="I4" t="n">
+        <v>324</v>
+      </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="K4" t="n">
-        <v>338.1</v>
+        <v>1087</v>
       </c>
       <c r="L4" t="n">
-        <v>245.5</v>
+        <v>18.7</v>
       </c>
       <c r="M4" t="n">
-        <v>290.6</v>
+        <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>874.2</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>61.6</v>
+        <v>45.7</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.8</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>75.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>24.3</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>24.0641711229947</v>
       </c>
       <c r="X4" t="n">
-        <v>27.65</v>
+        <v>23.2857506244092</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.16887417218543</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>27.2154316271963</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>26.9211850934372</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -983,24 +954,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2246</v>
+        <v>474</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1008,77 +970,79 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>76.92898734377771</v>
+        <v>78.2075977577509</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>27.6816608996539</v>
       </c>
       <c r="E5" t="n">
-        <v>22.7244034844085</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>49</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="I5" t="n">
+        <v>222</v>
+      </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>221</v>
       </c>
       <c r="K5" t="n">
-        <v>225.3</v>
+        <v>630</v>
       </c>
       <c r="L5" t="n">
-        <v>178.6</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
-        <v>267.7</v>
+        <v>25</v>
       </c>
       <c r="N5" t="n">
-        <v>671.6</v>
+        <v>23</v>
       </c>
       <c r="O5" t="n">
-        <v>25.6</v>
+        <v>59</v>
       </c>
       <c r="P5" t="n">
-        <v>90.3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>211.9</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>54.7</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>63.1</v>
+        <v>26.8</v>
       </c>
       <c r="V5" t="n">
-        <v>117.8</v>
+        <v>0.21</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X5" t="n">
-        <v>24.5</v>
+        <v>26.4345313179585</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.298611111111111</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>24.6052966641202</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.9831715115263</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1090,39 +1054,28 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>168</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1130,79 +1083,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>78.96926572362921</v>
+        <v>80.4444026161685</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>38.7396694214876</v>
       </c>
       <c r="E6" t="n">
-        <v>27.7551020408163</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
+        <v>966</v>
       </c>
       <c r="I6" t="n">
-        <v>152</v>
+        <v>1037</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>221</v>
       </c>
       <c r="K6" t="n">
-        <v>114</v>
+        <v>2224</v>
       </c>
       <c r="L6" t="n">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="M6" t="n">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="N6" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="O6" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>46</v>
+        <v>29.95</v>
       </c>
       <c r="V6" t="n">
-        <v>46</v>
+        <v>0.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>31.5126050420168</v>
       </c>
       <c r="X6" t="n">
-        <v>21.3</v>
+        <v>30.3986119121575</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3359375</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4357677787856</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1214,39 +1167,28 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>180</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AK6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1572</v>
+        <v>2447</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,88 +1196,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.5638272872462</v>
+        <v>88.5101123659594</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>23.3354661447551</v>
       </c>
       <c r="E7" t="n">
-        <v>24.8015873015873</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>695.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1650</v>
+        <v>297.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>255.1</v>
       </c>
       <c r="K7" t="n">
-        <v>117.8</v>
+        <v>1248.3</v>
       </c>
       <c r="L7" t="n">
-        <v>166</v>
+        <v>55.8</v>
       </c>
       <c r="M7" t="n">
-        <v>264.6</v>
+        <v>25.2</v>
       </c>
       <c r="N7" t="n">
-        <v>548.4</v>
+        <v>34.4</v>
       </c>
       <c r="O7" t="n">
-        <v>7.3</v>
+        <v>115.4</v>
       </c>
       <c r="P7" t="n">
-        <v>40.5</v>
+        <v>42.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>66.2</v>
+        <v>6.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>19.1</v>
+        <v>25.6</v>
       </c>
       <c r="V7" t="n">
-        <v>19.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>26.2923351158645</v>
       </c>
       <c r="X7" t="n">
-        <v>24.4</v>
+        <v>25.8576553751625</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.165413533834587</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>24.5098039215686</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>24.1181250506758</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1344,7 +1286,7 @@
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -1353,19 +1295,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>192</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
